--- a/SubRES_TMPL/SubRES_Hydrogenupd2.xlsx
+++ b/SubRES_TMPL/SubRES_Hydrogenupd2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ee46c55b5fc2ded/Documents/Git/times-ireland-model/SubRES_TMPL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{449E45FE-C266-4EAC-82E5-69AFBF9B4767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{449E45FE-C266-4EAC-82E5-69AFBF9B4767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD81FA53-9CD4-422B-AA6A-32738584F86F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -138,7 +138,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="92">
   <si>
     <t>LimType</t>
   </si>
@@ -428,6 +428,12 @@
   </si>
   <si>
     <t>*10</t>
+  </si>
+  <si>
+    <t>*8</t>
+  </si>
+  <si>
+    <t>IMPOIL</t>
   </si>
 </sst>
 </file>
@@ -1135,10 +1141,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -5302,7 +5304,15 @@
       <c r="AM4" s="26"/>
     </row>
     <row r="5" spans="2:39" x14ac:dyDescent="0.3">
-      <c r="G5" s="26"/>
+      <c r="D5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E5" t="s">
+        <v>90</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>91</v>
+      </c>
       <c r="H5" s="26"/>
       <c r="I5" s="26"/>
       <c r="J5" s="26"/>

--- a/SubRES_TMPL/SubRES_Hydrogenupd2.xlsx
+++ b/SubRES_TMPL/SubRES_Hydrogenupd2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ee46c55b5fc2ded/Documents/Git/times-ireland-model/SubRES_TMPL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{449E45FE-C266-4EAC-82E5-69AFBF9B4767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD81FA53-9CD4-422B-AA6A-32738584F86F}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{449E45FE-C266-4EAC-82E5-69AFBF9B4767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8827EE25-B32F-4150-9902-DEB380BA2CAF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -424,16 +424,16 @@
     <t>ELC, BIO</t>
   </si>
   <si>
-    <t>IMPH2G*</t>
-  </si>
-  <si>
     <t>*10</t>
   </si>
   <si>
     <t>*8</t>
   </si>
   <si>
-    <t>IMPOIL</t>
+    <t>IMPOIL*,IMPGAS*</t>
+  </si>
+  <si>
+    <t>IMPELC*,IMPBIO*</t>
   </si>
 </sst>
 </file>
@@ -1141,6 +1141,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -5265,10 +5269,10 @@
         <v>84</v>
       </c>
       <c r="E4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G4" s="26" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H4" s="26"/>
       <c r="I4" s="26"/>
@@ -5308,7 +5312,7 @@
         <v>84</v>
       </c>
       <c r="E5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G5" s="26" t="s">
         <v>91</v>
